--- a/docs/Reel-Hangman-Question-Bank.xlsx
+++ b/docs/Reel-Hangman-Question-Bank.xlsx
@@ -8612,7 +8612,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -8689,18 +8689,21 @@
     </font>
     <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10.000000"/>
       <color rgb="FFBBA577"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color rgb="FFBDA77B"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -8785,7 +8788,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="0" pivotButton="0"/>
@@ -8829,10 +8832,13 @@
     <xf fontId="15" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="16" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="16" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="17" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="17" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="18" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13731,7 +13737,7 @@
       <c r="C257" s="14" t="s">
         <v>851</v>
       </c>
-      <c r="D257" s="16" t="s">
+      <c r="D257" s="17" t="s">
         <v>852</v>
       </c>
       <c r="E257" s="14" t="s">
@@ -13746,13 +13752,13 @@
         <v>823</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>823</v>
-      </c>
-      <c r="D258" s="16" t="s">
         <v>854</v>
       </c>
+      <c r="D258" s="17" t="s">
+        <v>855</v>
+      </c>
       <c r="E258" s="14" t="s">
-        <v>855</v>
+        <v>9</v>
       </c>
     </row>
     <row r="259" ht="14.25">
@@ -17799,7 +17805,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1530</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -17808,7 +17814,7 @@
       <c r="C2" s="9" t="s">
         <v>1532</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>1533</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -17816,7 +17822,7 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>1534</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -17825,7 +17831,7 @@
       <c r="C3" s="9" t="s">
         <v>1536</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>1537</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -17833,7 +17839,7 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>1538</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -17842,7 +17848,7 @@
       <c r="C4" s="9" t="s">
         <v>1540</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>1541</v>
       </c>
       <c r="E4" s="11" t="s">
@@ -17850,7 +17856,7 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>1542</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -17859,7 +17865,7 @@
       <c r="C5" s="9" t="s">
         <v>1544</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>1545</v>
       </c>
       <c r="E5" s="11" t="s">
@@ -17867,7 +17873,7 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>1546</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -17876,7 +17882,7 @@
       <c r="C6" s="9" t="s">
         <v>1548</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>1549</v>
       </c>
       <c r="E6" s="11" t="s">
@@ -17884,7 +17890,7 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>1550</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -17893,7 +17899,7 @@
       <c r="C7" s="9" t="s">
         <v>1552</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>1553</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -17901,7 +17907,7 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>1554</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -17910,7 +17916,7 @@
       <c r="C8" s="9" t="s">
         <v>1556</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>1557</v>
       </c>
       <c r="E8" s="11" t="s">
@@ -17918,7 +17924,7 @@
       </c>
     </row>
     <row r="9" ht="31" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>1558</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -17927,7 +17933,7 @@
       <c r="C9" s="9" t="s">
         <v>1560</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>1561</v>
       </c>
       <c r="E9" s="11" t="s">
@@ -17935,7 +17941,7 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>1562</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -17944,7 +17950,7 @@
       <c r="C10" s="9" t="s">
         <v>1564</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>1565</v>
       </c>
       <c r="E10" s="11" t="s">
@@ -17952,7 +17958,7 @@
       </c>
     </row>
     <row r="11" ht="31" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>1566</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -17961,7 +17967,7 @@
       <c r="C11" s="9" t="s">
         <v>1568</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>1569</v>
       </c>
       <c r="E11" s="11" t="s">
@@ -17969,7 +17975,7 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>1570</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -17978,7 +17984,7 @@
       <c r="C12" s="9" t="s">
         <v>1572</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>1573</v>
       </c>
       <c r="E12" s="11" t="s">
@@ -17986,7 +17992,7 @@
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>1574</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -17995,7 +18001,7 @@
       <c r="C13" s="9" t="s">
         <v>1576</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>1577</v>
       </c>
       <c r="E13" s="11" t="s">
@@ -18003,7 +18009,7 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>1578</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -18012,7 +18018,7 @@
       <c r="C14" s="9" t="s">
         <v>1580</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>1581</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -18020,7 +18026,7 @@
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>1582</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -18029,7 +18035,7 @@
       <c r="C15" s="9" t="s">
         <v>1584</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>1585</v>
       </c>
       <c r="E15" s="11" t="s">
@@ -18037,7 +18043,7 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>1586</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -18046,7 +18052,7 @@
       <c r="C16" s="9" t="s">
         <v>1588</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>1589</v>
       </c>
       <c r="E16" s="11" t="s">
@@ -18054,7 +18060,7 @@
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>1590</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -18063,7 +18069,7 @@
       <c r="C17" s="9" t="s">
         <v>1592</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>1593</v>
       </c>
       <c r="E17" s="11" t="s">
@@ -18071,7 +18077,7 @@
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>1594</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -18080,7 +18086,7 @@
       <c r="C18" s="9" t="s">
         <v>1596</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>1597</v>
       </c>
       <c r="E18" s="11" t="s">
@@ -18088,7 +18094,7 @@
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>1598</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -18097,7 +18103,7 @@
       <c r="C19" s="9" t="s">
         <v>1600</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>1601</v>
       </c>
       <c r="E19" s="11" t="s">
@@ -18105,7 +18111,7 @@
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>1602</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -18114,7 +18120,7 @@
       <c r="C20" s="9" t="s">
         <v>1604</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>1605</v>
       </c>
       <c r="E20" s="11" t="s">
@@ -18122,7 +18128,7 @@
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>1606</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -18131,7 +18137,7 @@
       <c r="C21" s="9" t="s">
         <v>1608</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>1609</v>
       </c>
       <c r="E21" s="11" t="s">
@@ -18139,7 +18145,7 @@
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>1610</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -18148,7 +18154,7 @@
       <c r="C22" s="9" t="s">
         <v>1612</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>1613</v>
       </c>
       <c r="E22" s="11" t="s">
@@ -18156,7 +18162,7 @@
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>1614</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -18165,7 +18171,7 @@
       <c r="C23" s="9" t="s">
         <v>1616</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="19" t="s">
         <v>1617</v>
       </c>
       <c r="E23" s="11" t="s">
@@ -18173,7 +18179,7 @@
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>1618</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -18182,7 +18188,7 @@
       <c r="C24" s="9" t="s">
         <v>1620</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="19" t="s">
         <v>1621</v>
       </c>
       <c r="E24" s="11" t="s">
@@ -18190,7 +18196,7 @@
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>1622</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -18199,7 +18205,7 @@
       <c r="C25" s="9" t="s">
         <v>1624</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="19" t="s">
         <v>1625</v>
       </c>
       <c r="E25" s="11" t="s">
@@ -18207,7 +18213,7 @@
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>1626</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -18216,7 +18222,7 @@
       <c r="C26" s="9" t="s">
         <v>1628</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="19" t="s">
         <v>1629</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -18224,7 +18230,7 @@
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>1630</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -18233,7 +18239,7 @@
       <c r="C27" s="9" t="s">
         <v>1632</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="19" t="s">
         <v>1633</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -18241,7 +18247,7 @@
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>1634</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -18250,7 +18256,7 @@
       <c r="C28" s="9" t="s">
         <v>1636</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="19" t="s">
         <v>1637</v>
       </c>
       <c r="E28" s="12" t="s">
@@ -18258,7 +18264,7 @@
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>1638</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -18267,7 +18273,7 @@
       <c r="C29" s="9" t="s">
         <v>1640</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="19" t="s">
         <v>1641</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -18275,7 +18281,7 @@
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>1642</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -18284,7 +18290,7 @@
       <c r="C30" s="9" t="s">
         <v>1644</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="19" t="s">
         <v>1645</v>
       </c>
       <c r="E30" s="12" t="s">
@@ -18292,7 +18298,7 @@
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>1646</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -18301,7 +18307,7 @@
       <c r="C31" s="9" t="s">
         <v>1648</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="19" t="s">
         <v>1649</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -18309,7 +18315,7 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
         <v>1650</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -18318,7 +18324,7 @@
       <c r="C32" s="9" t="s">
         <v>1652</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="19" t="s">
         <v>1653</v>
       </c>
       <c r="E32" s="12" t="s">
@@ -18326,7 +18332,7 @@
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>1654</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -18335,7 +18341,7 @@
       <c r="C33" s="9" t="s">
         <v>1656</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="19" t="s">
         <v>1657</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -18343,7 +18349,7 @@
       </c>
     </row>
     <row r="34" ht="31" customHeight="1">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
         <v>1658</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -18352,7 +18358,7 @@
       <c r="C34" s="9" t="s">
         <v>1660</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="19" t="s">
         <v>1661</v>
       </c>
       <c r="E34" s="12" t="s">
@@ -18360,7 +18366,7 @@
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>1662</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -18369,7 +18375,7 @@
       <c r="C35" s="9" t="s">
         <v>1664</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="19" t="s">
         <v>1665</v>
       </c>
       <c r="E35" s="12" t="s">
@@ -18377,7 +18383,7 @@
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="18" t="s">
         <v>1666</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -18386,7 +18392,7 @@
       <c r="C36" s="9" t="s">
         <v>1668</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="19" t="s">
         <v>1669</v>
       </c>
       <c r="E36" s="12" t="s">
@@ -18394,7 +18400,7 @@
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="18" t="s">
         <v>1670</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -18403,7 +18409,7 @@
       <c r="C37" s="9" t="s">
         <v>1672</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="19" t="s">
         <v>1673</v>
       </c>
       <c r="E37" s="12" t="s">
@@ -18411,7 +18417,7 @@
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>1674</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -18420,7 +18426,7 @@
       <c r="C38" s="9" t="s">
         <v>1676</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="19" t="s">
         <v>1677</v>
       </c>
       <c r="E38" s="12" t="s">
@@ -18428,7 +18434,7 @@
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="18" t="s">
         <v>1678</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -18437,7 +18443,7 @@
       <c r="C39" s="9" t="s">
         <v>1680</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="19" t="s">
         <v>1681</v>
       </c>
       <c r="E39" s="12" t="s">
@@ -18445,7 +18451,7 @@
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="18" t="s">
         <v>1682</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -18454,7 +18460,7 @@
       <c r="C40" s="9" t="s">
         <v>1684</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="19" t="s">
         <v>1685</v>
       </c>
       <c r="E40" s="12" t="s">
@@ -18462,7 +18468,7 @@
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>1686</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -18471,7 +18477,7 @@
       <c r="C41" s="9" t="s">
         <v>1688</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="19" t="s">
         <v>1689</v>
       </c>
       <c r="E41" s="12" t="s">
@@ -18479,7 +18485,7 @@
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="18" t="s">
         <v>1690</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -18488,7 +18494,7 @@
       <c r="C42" s="9" t="s">
         <v>1692</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="19" t="s">
         <v>1693</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -18496,7 +18502,7 @@
       </c>
     </row>
     <row r="43" ht="31" customHeight="1">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="18" t="s">
         <v>1694</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -18505,7 +18511,7 @@
       <c r="C43" s="9" t="s">
         <v>1696</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="19" t="s">
         <v>1697</v>
       </c>
       <c r="E43" s="12" t="s">
@@ -18513,7 +18519,7 @@
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="18" t="s">
         <v>1698</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -18522,7 +18528,7 @@
       <c r="C44" s="9" t="s">
         <v>1700</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="19" t="s">
         <v>1701</v>
       </c>
       <c r="E44" s="12" t="s">
@@ -18530,7 +18536,7 @@
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="18" t="s">
         <v>1702</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -18539,7 +18545,7 @@
       <c r="C45" s="9" t="s">
         <v>1704</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="19" t="s">
         <v>1705</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -18547,7 +18553,7 @@
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="18" t="s">
         <v>1706</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -18556,7 +18562,7 @@
       <c r="C46" s="9" t="s">
         <v>1708</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="19" t="s">
         <v>1709</v>
       </c>
       <c r="E46" s="12" t="s">
@@ -18564,7 +18570,7 @@
       </c>
     </row>
     <row r="47" ht="31" customHeight="1">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="18" t="s">
         <v>1710</v>
       </c>
       <c r="B47" s="8" t="s">
@@ -18573,7 +18579,7 @@
       <c r="C47" s="9" t="s">
         <v>1712</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="19" t="s">
         <v>1713</v>
       </c>
       <c r="E47" s="12" t="s">
@@ -18581,7 +18587,7 @@
       </c>
     </row>
     <row r="48" ht="31" customHeight="1">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="18" t="s">
         <v>1714</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -18590,7 +18596,7 @@
       <c r="C48" s="9" t="s">
         <v>1716</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="19" t="s">
         <v>1717</v>
       </c>
       <c r="E48" s="12" t="s">
@@ -18598,7 +18604,7 @@
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="18" t="s">
         <v>1718</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -18607,7 +18613,7 @@
       <c r="C49" s="9" t="s">
         <v>1720</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="19" t="s">
         <v>1721</v>
       </c>
       <c r="E49" s="12" t="s">
@@ -18615,7 +18621,7 @@
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="18" t="s">
         <v>1722</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -18624,7 +18630,7 @@
       <c r="C50" s="9" t="s">
         <v>1724</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="19" t="s">
         <v>1725</v>
       </c>
       <c r="E50" s="12" t="s">
@@ -18632,7 +18638,7 @@
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="18" t="s">
         <v>1726</v>
       </c>
       <c r="B51" s="8" t="s">
@@ -18641,7 +18647,7 @@
       <c r="C51" s="9" t="s">
         <v>1728</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="19" t="s">
         <v>1729</v>
       </c>
       <c r="E51" s="12" t="s">
@@ -18649,7 +18655,7 @@
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="18" t="s">
         <v>1730</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -18658,7 +18664,7 @@
       <c r="C52" s="9" t="s">
         <v>1732</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="19" t="s">
         <v>1733</v>
       </c>
       <c r="E52" s="12" t="s">
@@ -18666,7 +18672,7 @@
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="18" t="s">
         <v>1734</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -18675,7 +18681,7 @@
       <c r="C53" s="9" t="s">
         <v>1736</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="19" t="s">
         <v>1737</v>
       </c>
       <c r="E53" s="12" t="s">
@@ -18683,7 +18689,7 @@
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="18" t="s">
         <v>1738</v>
       </c>
       <c r="B54" s="8" t="s">
@@ -18692,7 +18698,7 @@
       <c r="C54" s="9" t="s">
         <v>1740</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D54" s="19" t="s">
         <v>1741</v>
       </c>
       <c r="E54" s="12" t="s">
@@ -18700,7 +18706,7 @@
       </c>
     </row>
     <row r="55" ht="31" customHeight="1">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="18" t="s">
         <v>1742</v>
       </c>
       <c r="B55" s="8" t="s">
@@ -18709,7 +18715,7 @@
       <c r="C55" s="9" t="s">
         <v>1744</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D55" s="19" t="s">
         <v>1745</v>
       </c>
       <c r="E55" s="12" t="s">
@@ -18717,7 +18723,7 @@
       </c>
     </row>
     <row r="56" ht="26" customHeight="1">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="18" t="s">
         <v>1746</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -18726,7 +18732,7 @@
       <c r="C56" s="9" t="s">
         <v>1748</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="19" t="s">
         <v>1749</v>
       </c>
       <c r="E56" s="12" t="s">
@@ -18734,7 +18740,7 @@
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="18" t="s">
         <v>1750</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -18743,7 +18749,7 @@
       <c r="C57" s="9" t="s">
         <v>1752</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="19" t="s">
         <v>1753</v>
       </c>
       <c r="E57" s="12" t="s">
@@ -18751,7 +18757,7 @@
       </c>
     </row>
     <row r="58" ht="31" customHeight="1">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="18" t="s">
         <v>1754</v>
       </c>
       <c r="B58" s="8" t="s">
@@ -18760,7 +18766,7 @@
       <c r="C58" s="9" t="s">
         <v>1756</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="19" t="s">
         <v>1757</v>
       </c>
       <c r="E58" s="12" t="s">
@@ -18768,7 +18774,7 @@
       </c>
     </row>
     <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="18" t="s">
         <v>1758</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -18777,7 +18783,7 @@
       <c r="C59" s="9" t="s">
         <v>1760</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="D59" s="19" t="s">
         <v>1761</v>
       </c>
       <c r="E59" s="12" t="s">
@@ -18785,7 +18791,7 @@
       </c>
     </row>
     <row r="60" ht="31" customHeight="1">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="18" t="s">
         <v>1762</v>
       </c>
       <c r="B60" s="8" t="s">
@@ -18794,7 +18800,7 @@
       <c r="C60" s="9" t="s">
         <v>1764</v>
       </c>
-      <c r="D60" s="18" t="s">
+      <c r="D60" s="19" t="s">
         <v>1765</v>
       </c>
       <c r="E60" s="12" t="s">
@@ -18802,7 +18808,7 @@
       </c>
     </row>
     <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="17" t="s">
+      <c r="A61" s="18" t="s">
         <v>1766</v>
       </c>
       <c r="B61" s="8" t="s">
@@ -18811,7 +18817,7 @@
       <c r="C61" s="9" t="s">
         <v>1768</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="D61" s="19" t="s">
         <v>1769</v>
       </c>
       <c r="E61" s="12" t="s">
@@ -18819,7 +18825,7 @@
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="18" t="s">
         <v>1770</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -18828,7 +18834,7 @@
       <c r="C62" s="9" t="s">
         <v>1772</v>
       </c>
-      <c r="D62" s="18" t="s">
+      <c r="D62" s="19" t="s">
         <v>1773</v>
       </c>
       <c r="E62" s="12" t="s">
@@ -18836,7 +18842,7 @@
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="18" t="s">
         <v>1774</v>
       </c>
       <c r="B63" s="8" t="s">
@@ -18845,7 +18851,7 @@
       <c r="C63" s="9" t="s">
         <v>1776</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="D63" s="19" t="s">
         <v>1777</v>
       </c>
       <c r="E63" s="12" t="s">
@@ -18853,7 +18859,7 @@
       </c>
     </row>
     <row r="64" ht="26" customHeight="1">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="18" t="s">
         <v>1778</v>
       </c>
       <c r="B64" s="8" t="s">
@@ -18862,7 +18868,7 @@
       <c r="C64" s="9" t="s">
         <v>1780</v>
       </c>
-      <c r="D64" s="18" t="s">
+      <c r="D64" s="19" t="s">
         <v>1781</v>
       </c>
       <c r="E64" s="12" t="s">
@@ -18870,7 +18876,7 @@
       </c>
     </row>
     <row r="65" ht="26" customHeight="1">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="18" t="s">
         <v>1782</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -18879,7 +18885,7 @@
       <c r="C65" s="9" t="s">
         <v>1784</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="D65" s="19" t="s">
         <v>1785</v>
       </c>
       <c r="E65" s="12" t="s">
@@ -18887,7 +18893,7 @@
       </c>
     </row>
     <row r="66" ht="26" customHeight="1">
-      <c r="A66" s="17" t="s">
+      <c r="A66" s="18" t="s">
         <v>1786</v>
       </c>
       <c r="B66" s="8" t="s">
@@ -18896,7 +18902,7 @@
       <c r="C66" s="9" t="s">
         <v>1788</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="D66" s="19" t="s">
         <v>1789</v>
       </c>
       <c r="E66" s="12" t="s">
@@ -18904,7 +18910,7 @@
       </c>
     </row>
     <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="17" t="s">
+      <c r="A67" s="18" t="s">
         <v>1790</v>
       </c>
       <c r="B67" s="8" t="s">
@@ -18913,7 +18919,7 @@
       <c r="C67" s="9" t="s">
         <v>1792</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="D67" s="19" t="s">
         <v>1793</v>
       </c>
       <c r="E67" s="12" t="s">
@@ -18921,7 +18927,7 @@
       </c>
     </row>
     <row r="68" ht="26" customHeight="1">
-      <c r="A68" s="17" t="s">
+      <c r="A68" s="18" t="s">
         <v>1794</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -18930,7 +18936,7 @@
       <c r="C68" s="9" t="s">
         <v>1796</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="D68" s="19" t="s">
         <v>1797</v>
       </c>
       <c r="E68" s="12" t="s">
@@ -18938,7 +18944,7 @@
       </c>
     </row>
     <row r="69" ht="26" customHeight="1">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="18" t="s">
         <v>1798</v>
       </c>
       <c r="B69" s="8" t="s">
@@ -18947,7 +18953,7 @@
       <c r="C69" s="9" t="s">
         <v>1800</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="D69" s="19" t="s">
         <v>1801</v>
       </c>
       <c r="E69" s="12" t="s">
@@ -18955,7 +18961,7 @@
       </c>
     </row>
     <row r="70" ht="26" customHeight="1">
-      <c r="A70" s="17" t="s">
+      <c r="A70" s="18" t="s">
         <v>1802</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -18964,7 +18970,7 @@
       <c r="C70" s="9" t="s">
         <v>1804</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="D70" s="19" t="s">
         <v>1805</v>
       </c>
       <c r="E70" s="12" t="s">
@@ -18972,7 +18978,7 @@
       </c>
     </row>
     <row r="71" ht="31" customHeight="1">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="18" t="s">
         <v>1806</v>
       </c>
       <c r="B71" s="8" t="s">
@@ -18981,7 +18987,7 @@
       <c r="C71" s="9" t="s">
         <v>1808</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D71" s="19" t="s">
         <v>1809</v>
       </c>
       <c r="E71" s="12" t="s">
@@ -18989,7 +18995,7 @@
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="18" t="s">
         <v>1810</v>
       </c>
       <c r="B72" s="8" t="s">
@@ -18998,7 +19004,7 @@
       <c r="C72" s="9" t="s">
         <v>1812</v>
       </c>
-      <c r="D72" s="18" t="s">
+      <c r="D72" s="19" t="s">
         <v>1813</v>
       </c>
       <c r="E72" s="12" t="s">
@@ -19006,7 +19012,7 @@
       </c>
     </row>
     <row r="73" ht="31" customHeight="1">
-      <c r="A73" s="17" t="s">
+      <c r="A73" s="18" t="s">
         <v>1814</v>
       </c>
       <c r="B73" s="8" t="s">
@@ -19015,7 +19021,7 @@
       <c r="C73" s="9" t="s">
         <v>1816</v>
       </c>
-      <c r="D73" s="18" t="s">
+      <c r="D73" s="19" t="s">
         <v>1817</v>
       </c>
       <c r="E73" s="13" t="s">
@@ -19023,7 +19029,7 @@
       </c>
     </row>
     <row r="74" ht="26" customHeight="1">
-      <c r="A74" s="17" t="s">
+      <c r="A74" s="18" t="s">
         <v>1818</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -19032,7 +19038,7 @@
       <c r="C74" s="9" t="s">
         <v>1820</v>
       </c>
-      <c r="D74" s="18" t="s">
+      <c r="D74" s="19" t="s">
         <v>1821</v>
       </c>
       <c r="E74" s="13" t="s">
@@ -19040,7 +19046,7 @@
       </c>
     </row>
     <row r="75" ht="26" customHeight="1">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="18" t="s">
         <v>1822</v>
       </c>
       <c r="B75" s="8" t="s">
@@ -19049,7 +19055,7 @@
       <c r="C75" s="9" t="s">
         <v>1824</v>
       </c>
-      <c r="D75" s="18" t="s">
+      <c r="D75" s="19" t="s">
         <v>1825</v>
       </c>
       <c r="E75" s="13" t="s">
@@ -19057,7 +19063,7 @@
       </c>
     </row>
     <row r="76" ht="26" customHeight="1">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="18" t="s">
         <v>1826</v>
       </c>
       <c r="B76" s="8" t="s">
@@ -19066,7 +19072,7 @@
       <c r="C76" s="9" t="s">
         <v>1828</v>
       </c>
-      <c r="D76" s="18" t="s">
+      <c r="D76" s="19" t="s">
         <v>1829</v>
       </c>
       <c r="E76" s="13" t="s">
@@ -19074,7 +19080,7 @@
       </c>
     </row>
     <row r="77" ht="31" customHeight="1">
-      <c r="A77" s="17" t="s">
+      <c r="A77" s="18" t="s">
         <v>1830</v>
       </c>
       <c r="B77" s="8" t="s">
@@ -19083,7 +19089,7 @@
       <c r="C77" s="9" t="s">
         <v>1832</v>
       </c>
-      <c r="D77" s="18" t="s">
+      <c r="D77" s="19" t="s">
         <v>1833</v>
       </c>
       <c r="E77" s="13" t="s">
@@ -19135,7 +19141,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1835</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -19144,7 +19150,7 @@
       <c r="C2" s="9" t="s">
         <v>1837</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>1838</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -19152,7 +19158,7 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>1839</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -19161,7 +19167,7 @@
       <c r="C3" s="9" t="s">
         <v>1841</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>1842</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -19169,7 +19175,7 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>1843</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -19178,7 +19184,7 @@
       <c r="C4" s="9" t="s">
         <v>1845</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>1846</v>
       </c>
       <c r="E4" s="11" t="s">
@@ -19186,7 +19192,7 @@
       </c>
     </row>
     <row r="5" ht="31" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>1847</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -19195,7 +19201,7 @@
       <c r="C5" s="9" t="s">
         <v>1849</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>1850</v>
       </c>
       <c r="E5" s="11" t="s">
@@ -19203,7 +19209,7 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>1851</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -19212,7 +19218,7 @@
       <c r="C6" s="9" t="s">
         <v>1853</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>1854</v>
       </c>
       <c r="E6" s="11" t="s">
@@ -19220,7 +19226,7 @@
       </c>
     </row>
     <row r="7" ht="31" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>1855</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -19229,7 +19235,7 @@
       <c r="C7" s="9" t="s">
         <v>1857</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>1858</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -19237,7 +19243,7 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>1859</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -19246,7 +19252,7 @@
       <c r="C8" s="9" t="s">
         <v>1861</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>1862</v>
       </c>
       <c r="E8" s="11" t="s">
@@ -19254,7 +19260,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>1863</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -19263,7 +19269,7 @@
       <c r="C9" s="9" t="s">
         <v>1865</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>1866</v>
       </c>
       <c r="E9" s="11" t="s">
@@ -19271,7 +19277,7 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>1867</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -19280,7 +19286,7 @@
       <c r="C10" s="9" t="s">
         <v>1869</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>1870</v>
       </c>
       <c r="E10" s="11" t="s">
@@ -19288,7 +19294,7 @@
       </c>
     </row>
     <row r="11" ht="31" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>1871</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -19297,7 +19303,7 @@
       <c r="C11" s="9" t="s">
         <v>1873</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>1874</v>
       </c>
       <c r="E11" s="11" t="s">
@@ -19305,7 +19311,7 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>1875</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -19314,7 +19320,7 @@
       <c r="C12" s="9" t="s">
         <v>1877</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>1878</v>
       </c>
       <c r="E12" s="11" t="s">
@@ -19322,7 +19328,7 @@
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>1879</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -19331,7 +19337,7 @@
       <c r="C13" s="9" t="s">
         <v>1881</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>1882</v>
       </c>
       <c r="E13" s="11" t="s">
@@ -19339,7 +19345,7 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>1883</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -19348,7 +19354,7 @@
       <c r="C14" s="9" t="s">
         <v>1885</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>1886</v>
       </c>
       <c r="E14" s="12" t="s">
@@ -19356,7 +19362,7 @@
       </c>
     </row>
     <row r="15" ht="31" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>1887</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -19365,7 +19371,7 @@
       <c r="C15" s="9" t="s">
         <v>1889</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>1890</v>
       </c>
       <c r="E15" s="12" t="s">
@@ -19373,7 +19379,7 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>1891</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -19382,7 +19388,7 @@
       <c r="C16" s="9" t="s">
         <v>1893</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>1894</v>
       </c>
       <c r="E16" s="12" t="s">
@@ -19390,7 +19396,7 @@
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>1895</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -19399,7 +19405,7 @@
       <c r="C17" s="9" t="s">
         <v>1897</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>1898</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -19407,7 +19413,7 @@
       </c>
     </row>
     <row r="18" ht="31" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>1899</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -19416,7 +19422,7 @@
       <c r="C18" s="9" t="s">
         <v>1901</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>1902</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -19424,7 +19430,7 @@
       </c>
     </row>
     <row r="19" ht="31" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>1903</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -19433,7 +19439,7 @@
       <c r="C19" s="9" t="s">
         <v>1905</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>1906</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -19441,7 +19447,7 @@
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>1907</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -19450,7 +19456,7 @@
       <c r="C20" s="9" t="s">
         <v>1909</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>1910</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -19458,7 +19464,7 @@
       </c>
     </row>
     <row r="21" ht="31" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>1911</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -19467,7 +19473,7 @@
       <c r="C21" s="9" t="s">
         <v>1913</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>1914</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -19475,7 +19481,7 @@
       </c>
     </row>
     <row r="22" ht="31" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>1915</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -19484,7 +19490,7 @@
       <c r="C22" s="9" t="s">
         <v>1917</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>916</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -19492,7 +19498,7 @@
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>1918</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -19501,7 +19507,7 @@
       <c r="C23" s="9" t="s">
         <v>1920</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="19" t="s">
         <v>1921</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -19509,7 +19515,7 @@
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>1922</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -19518,7 +19524,7 @@
       <c r="C24" s="9" t="s">
         <v>1924</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="19" t="s">
         <v>1925</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -19526,7 +19532,7 @@
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>1926</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -19535,7 +19541,7 @@
       <c r="C25" s="9" t="s">
         <v>1928</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="19" t="s">
         <v>1929</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -19543,7 +19549,7 @@
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>1930</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -19552,7 +19558,7 @@
       <c r="C26" s="9" t="s">
         <v>1932</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="19" t="s">
         <v>1933</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -19560,7 +19566,7 @@
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>1934</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -19569,7 +19575,7 @@
       <c r="C27" s="9" t="s">
         <v>1936</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="19" t="s">
         <v>1937</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -19577,7 +19583,7 @@
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>1938</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -19586,7 +19592,7 @@
       <c r="C28" s="9" t="s">
         <v>1940</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="19" t="s">
         <v>976</v>
       </c>
       <c r="E28" s="12" t="s">
@@ -19594,7 +19600,7 @@
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>1941</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -19603,7 +19609,7 @@
       <c r="C29" s="9" t="s">
         <v>1943</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="19" t="s">
         <v>913</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -19611,7 +19617,7 @@
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>1944</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -19620,7 +19626,7 @@
       <c r="C30" s="9" t="s">
         <v>1946</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="19" t="s">
         <v>1947</v>
       </c>
       <c r="E30" s="12" t="s">
@@ -19628,7 +19634,7 @@
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>1948</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -19637,7 +19643,7 @@
       <c r="C31" s="9" t="s">
         <v>1950</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="19" t="s">
         <v>1951</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -19645,7 +19651,7 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
         <v>1952</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -19654,7 +19660,7 @@
       <c r="C32" s="9" t="s">
         <v>1954</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="19" t="s">
         <v>1955</v>
       </c>
       <c r="E32" s="12" t="s">
@@ -19662,7 +19668,7 @@
       </c>
     </row>
     <row r="33" ht="31" customHeight="1">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>1956</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -19671,7 +19677,7 @@
       <c r="C33" s="9" t="s">
         <v>1958</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="19" t="s">
         <v>1959</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -19679,7 +19685,7 @@
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
         <v>1960</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -19688,7 +19694,7 @@
       <c r="C34" s="9" t="s">
         <v>1962</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="19" t="s">
         <v>1963</v>
       </c>
       <c r="E34" s="12" t="s">
@@ -19696,7 +19702,7 @@
       </c>
     </row>
     <row r="35" ht="31" customHeight="1">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>1964</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -19705,7 +19711,7 @@
       <c r="C35" s="9" t="s">
         <v>1966</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="19" t="s">
         <v>1967</v>
       </c>
       <c r="E35" s="12" t="s">
@@ -19713,7 +19719,7 @@
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="18" t="s">
         <v>1968</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -19722,7 +19728,7 @@
       <c r="C36" s="9" t="s">
         <v>1970</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="19" t="s">
         <v>1971</v>
       </c>
       <c r="E36" s="12" t="s">
@@ -19730,7 +19736,7 @@
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="18" t="s">
         <v>1972</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -19739,7 +19745,7 @@
       <c r="C37" s="9" t="s">
         <v>1974</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="19" t="s">
         <v>1975</v>
       </c>
       <c r="E37" s="12" t="s">
@@ -19747,7 +19753,7 @@
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>1976</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -19756,7 +19762,7 @@
       <c r="C38" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="19" t="s">
         <v>1979</v>
       </c>
       <c r="E38" s="12" t="s">
@@ -19764,7 +19770,7 @@
       </c>
     </row>
     <row r="39" ht="31" customHeight="1">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="18" t="s">
         <v>1980</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -19773,7 +19779,7 @@
       <c r="C39" s="9" t="s">
         <v>1982</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="19" t="s">
         <v>1983</v>
       </c>
       <c r="E39" s="12" t="s">
@@ -19781,7 +19787,7 @@
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="18" t="s">
         <v>1984</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -19790,7 +19796,7 @@
       <c r="C40" s="9" t="s">
         <v>1986</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="19" t="s">
         <v>1987</v>
       </c>
       <c r="E40" s="12" t="s">
@@ -19798,7 +19804,7 @@
       </c>
     </row>
     <row r="41" ht="31" customHeight="1">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>1988</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -19807,7 +19813,7 @@
       <c r="C41" s="9" t="s">
         <v>1990</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="19" t="s">
         <v>1991</v>
       </c>
       <c r="E41" s="12" t="s">
@@ -19815,7 +19821,7 @@
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="18" t="s">
         <v>1992</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -19824,7 +19830,7 @@
       <c r="C42" s="9" t="s">
         <v>1994</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="19" t="s">
         <v>1995</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -19832,7 +19838,7 @@
       </c>
     </row>
     <row r="43" ht="31" customHeight="1">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="18" t="s">
         <v>1996</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -19841,7 +19847,7 @@
       <c r="C43" s="9" t="s">
         <v>1998</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="19" t="s">
         <v>1999</v>
       </c>
       <c r="E43" s="12" t="s">
@@ -19849,7 +19855,7 @@
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="18" t="s">
         <v>2000</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -19858,7 +19864,7 @@
       <c r="C44" s="9" t="s">
         <v>2002</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="19" t="s">
         <v>2003</v>
       </c>
       <c r="E44" s="12" t="s">
@@ -19866,7 +19872,7 @@
       </c>
     </row>
     <row r="45" ht="31" customHeight="1">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="18" t="s">
         <v>2004</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -19875,7 +19881,7 @@
       <c r="C45" s="9" t="s">
         <v>2006</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="19" t="s">
         <v>2007</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -19883,7 +19889,7 @@
       </c>
     </row>
     <row r="46" ht="31" customHeight="1">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="18" t="s">
         <v>2008</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -19892,7 +19898,7 @@
       <c r="C46" s="9" t="s">
         <v>2010</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="19" t="s">
         <v>2011</v>
       </c>
       <c r="E46" s="12" t="s">
@@ -19900,7 +19906,7 @@
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="18" t="s">
         <v>2012</v>
       </c>
       <c r="B47" s="8" t="s">
@@ -19909,7 +19915,7 @@
       <c r="C47" s="9" t="s">
         <v>2014</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="19" t="s">
         <v>2015</v>
       </c>
       <c r="E47" s="12" t="s">
@@ -19917,7 +19923,7 @@
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="18" t="s">
         <v>2016</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -19926,7 +19932,7 @@
       <c r="C48" s="9" t="s">
         <v>2018</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="19" t="s">
         <v>2019</v>
       </c>
       <c r="E48" s="12" t="s">
@@ -19934,7 +19940,7 @@
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="18" t="s">
         <v>2020</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -19943,7 +19949,7 @@
       <c r="C49" s="9" t="s">
         <v>2022</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="19" t="s">
         <v>2023</v>
       </c>
       <c r="E49" s="13" t="s">
@@ -19951,7 +19957,7 @@
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="18" t="s">
         <v>2024</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -19960,7 +19966,7 @@
       <c r="C50" s="9" t="s">
         <v>2026</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="19" t="s">
         <v>2027</v>
       </c>
       <c r="E50" s="13" t="s">
@@ -19968,7 +19974,7 @@
       </c>
     </row>
     <row r="51" ht="31" customHeight="1">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="18" t="s">
         <v>2028</v>
       </c>
       <c r="B51" s="8" t="s">
@@ -19977,7 +19983,7 @@
       <c r="C51" s="9" t="s">
         <v>2030</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="19" t="s">
         <v>2031</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -19985,7 +19991,7 @@
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="18" t="s">
         <v>2032</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -19994,7 +20000,7 @@
       <c r="C52" s="9" t="s">
         <v>2034</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="19" t="s">
         <v>2035</v>
       </c>
       <c r="E52" s="13" t="s">
@@ -20002,7 +20008,7 @@
       </c>
     </row>
     <row r="53" ht="31" customHeight="1">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="18" t="s">
         <v>2036</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -20011,7 +20017,7 @@
       <c r="C53" s="9" t="s">
         <v>2038</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="19" t="s">
         <v>2039</v>
       </c>
       <c r="E53" s="13" t="s">
@@ -20019,7 +20025,7 @@
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="18" t="s">
         <v>2040</v>
       </c>
       <c r="B54" s="8" t="s">
@@ -20028,7 +20034,7 @@
       <c r="C54" s="9" t="s">
         <v>2042</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D54" s="19" t="s">
         <v>2043</v>
       </c>
       <c r="E54" s="13" t="s">
@@ -20080,7 +20086,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>2045</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -20089,7 +20095,7 @@
       <c r="C2" s="9" t="s">
         <v>2047</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>2048</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -20097,7 +20103,7 @@
       </c>
     </row>
     <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>2049</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -20106,7 +20112,7 @@
       <c r="C3" s="9" t="s">
         <v>2051</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>2052</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -20114,7 +20120,7 @@
       </c>
     </row>
     <row r="4" ht="31" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>2053</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -20123,7 +20129,7 @@
       <c r="C4" s="9" t="s">
         <v>2055</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>2056</v>
       </c>
       <c r="E4" s="11" t="s">
@@ -20131,7 +20137,7 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>2057</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -20140,7 +20146,7 @@
       <c r="C5" s="9" t="s">
         <v>2059</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>2060</v>
       </c>
       <c r="E5" s="11" t="s">
@@ -20148,7 +20154,7 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>2061</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -20157,7 +20163,7 @@
       <c r="C6" s="9" t="s">
         <v>2063</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>2064</v>
       </c>
       <c r="E6" s="11" t="s">
@@ -20165,7 +20171,7 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>2065</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -20174,7 +20180,7 @@
       <c r="C7" s="9" t="s">
         <v>2067</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>2068</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -20182,7 +20188,7 @@
       </c>
     </row>
     <row r="8" ht="31" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>2069</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -20191,7 +20197,7 @@
       <c r="C8" s="9" t="s">
         <v>2071</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>2072</v>
       </c>
       <c r="E8" s="11" t="s">
@@ -20199,7 +20205,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>2073</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -20208,7 +20214,7 @@
       <c r="C9" s="9" t="s">
         <v>2075</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>2076</v>
       </c>
       <c r="E9" s="11" t="s">
@@ -20216,7 +20222,7 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>2077</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -20225,7 +20231,7 @@
       <c r="C10" s="9" t="s">
         <v>2079</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>2080</v>
       </c>
       <c r="E10" s="11" t="s">
@@ -20233,7 +20239,7 @@
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>2081</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -20242,7 +20248,7 @@
       <c r="C11" s="9" t="s">
         <v>2083</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>2084</v>
       </c>
       <c r="E11" s="11" t="s">
@@ -20250,7 +20256,7 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>2085</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -20259,7 +20265,7 @@
       <c r="C12" s="9" t="s">
         <v>2087</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>2088</v>
       </c>
       <c r="E12" s="11" t="s">
@@ -20267,7 +20273,7 @@
       </c>
     </row>
     <row r="13" ht="31" customHeight="1">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>2089</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -20276,7 +20282,7 @@
       <c r="C13" s="9" t="s">
         <v>2091</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>2092</v>
       </c>
       <c r="E13" s="11" t="s">
@@ -20284,7 +20290,7 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>2093</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -20293,7 +20299,7 @@
       <c r="C14" s="9" t="s">
         <v>2095</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>2096</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -20301,7 +20307,7 @@
       </c>
     </row>
     <row r="15" ht="31" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>2097</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -20310,7 +20316,7 @@
       <c r="C15" s="9" t="s">
         <v>2099</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>2100</v>
       </c>
       <c r="E15" s="11" t="s">
@@ -20318,7 +20324,7 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>2101</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -20327,7 +20333,7 @@
       <c r="C16" s="9" t="s">
         <v>2103</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>2104</v>
       </c>
       <c r="E16" s="11" t="s">
@@ -20335,7 +20341,7 @@
       </c>
     </row>
     <row r="17" ht="31" customHeight="1">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>2105</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -20344,7 +20350,7 @@
       <c r="C17" s="9" t="s">
         <v>2107</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>2108</v>
       </c>
       <c r="E17" s="11" t="s">
@@ -20352,7 +20358,7 @@
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>2109</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -20361,7 +20367,7 @@
       <c r="C18" s="9" t="s">
         <v>2111</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>2112</v>
       </c>
       <c r="E18" s="11" t="s">
@@ -20369,7 +20375,7 @@
       </c>
     </row>
     <row r="19" ht="31" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>2113</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -20378,7 +20384,7 @@
       <c r="C19" s="9" t="s">
         <v>2115</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>2116</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -20386,7 +20392,7 @@
       </c>
     </row>
     <row r="20" ht="31" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>2117</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -20395,7 +20401,7 @@
       <c r="C20" s="9" t="s">
         <v>2119</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>2120</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -20403,7 +20409,7 @@
       </c>
     </row>
     <row r="21" ht="31" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>2121</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -20412,7 +20418,7 @@
       <c r="C21" s="9" t="s">
         <v>2123</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>2124</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -20420,7 +20426,7 @@
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>2125</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -20429,7 +20435,7 @@
       <c r="C22" s="9" t="s">
         <v>2127</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>2128</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -20437,7 +20443,7 @@
       </c>
     </row>
     <row r="23" ht="31" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>2129</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -20446,7 +20452,7 @@
       <c r="C23" s="9" t="s">
         <v>2131</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="19" t="s">
         <v>2132</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -20454,7 +20460,7 @@
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>2133</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -20463,7 +20469,7 @@
       <c r="C24" s="9" t="s">
         <v>2135</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="19" t="s">
         <v>2136</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -20471,7 +20477,7 @@
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>2137</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -20480,7 +20486,7 @@
       <c r="C25" s="9" t="s">
         <v>2139</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="19" t="s">
         <v>2140</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -20488,7 +20494,7 @@
       </c>
     </row>
     <row r="26" ht="31" customHeight="1">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>2141</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -20497,7 +20503,7 @@
       <c r="C26" s="9" t="s">
         <v>2143</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="19" t="s">
         <v>2144</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -20505,7 +20511,7 @@
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>2145</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -20514,7 +20520,7 @@
       <c r="C27" s="9" t="s">
         <v>2147</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="19" t="s">
         <v>2148</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -20522,7 +20528,7 @@
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>2149</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -20531,7 +20537,7 @@
       <c r="C28" s="9" t="s">
         <v>2151</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="19" t="s">
         <v>2152</v>
       </c>
       <c r="E28" s="12" t="s">
@@ -20539,7 +20545,7 @@
       </c>
     </row>
     <row r="29" ht="31" customHeight="1">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>2153</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -20548,7 +20554,7 @@
       <c r="C29" s="9" t="s">
         <v>2155</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="19" t="s">
         <v>2156</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -20556,7 +20562,7 @@
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>2157</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -20565,7 +20571,7 @@
       <c r="C30" s="9" t="s">
         <v>2159</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="19" t="s">
         <v>2160</v>
       </c>
       <c r="E30" s="12" t="s">
@@ -20573,7 +20579,7 @@
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>2161</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -20582,7 +20588,7 @@
       <c r="C31" s="9" t="s">
         <v>2163</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="19" t="s">
         <v>2164</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -20590,7 +20596,7 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
         <v>2165</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -20599,7 +20605,7 @@
       <c r="C32" s="9" t="s">
         <v>2167</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="19" t="s">
         <v>2168</v>
       </c>
       <c r="E32" s="12" t="s">
@@ -20607,7 +20613,7 @@
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>2169</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -20616,7 +20622,7 @@
       <c r="C33" s="9" t="s">
         <v>2171</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="19" t="s">
         <v>2172</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -20624,7 +20630,7 @@
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
         <v>2173</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -20633,7 +20639,7 @@
       <c r="C34" s="9" t="s">
         <v>2175</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="19" t="s">
         <v>2176</v>
       </c>
       <c r="E34" s="12" t="s">
@@ -20641,7 +20647,7 @@
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>2177</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -20650,7 +20656,7 @@
       <c r="C35" s="9" t="s">
         <v>2179</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="19" t="s">
         <v>2180</v>
       </c>
       <c r="E35" s="12" t="s">
@@ -20658,7 +20664,7 @@
       </c>
     </row>
     <row r="36" ht="31" customHeight="1">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="18" t="s">
         <v>2181</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -20667,7 +20673,7 @@
       <c r="C36" s="9" t="s">
         <v>2183</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="19" t="s">
         <v>2184</v>
       </c>
       <c r="E36" s="12" t="s">
@@ -20675,7 +20681,7 @@
       </c>
     </row>
     <row r="37" ht="31" customHeight="1">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="18" t="s">
         <v>2185</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -20684,7 +20690,7 @@
       <c r="C37" s="9" t="s">
         <v>2187</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="19" t="s">
         <v>2188</v>
       </c>
       <c r="E37" s="12" t="s">
@@ -20692,7 +20698,7 @@
       </c>
     </row>
     <row r="38" ht="31" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>2189</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -20701,7 +20707,7 @@
       <c r="C38" s="9" t="s">
         <v>2191</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="19" t="s">
         <v>2192</v>
       </c>
       <c r="E38" s="12" t="s">
@@ -20709,7 +20715,7 @@
       </c>
     </row>
     <row r="39" ht="31" customHeight="1">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="18" t="s">
         <v>2193</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -20718,7 +20724,7 @@
       <c r="C39" s="9" t="s">
         <v>2195</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="19" t="s">
         <v>2196</v>
       </c>
       <c r="E39" s="12" t="s">
@@ -20726,7 +20732,7 @@
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="18" t="s">
         <v>2197</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -20735,7 +20741,7 @@
       <c r="C40" s="9" t="s">
         <v>2199</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="19" t="s">
         <v>2200</v>
       </c>
       <c r="E40" s="12" t="s">
@@ -20743,7 +20749,7 @@
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>2201</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -20752,7 +20758,7 @@
       <c r="C41" s="9" t="s">
         <v>2203</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="19" t="s">
         <v>2204</v>
       </c>
       <c r="E41" s="12" t="s">
@@ -20760,7 +20766,7 @@
       </c>
     </row>
     <row r="42" ht="31" customHeight="1">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="18" t="s">
         <v>2205</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -20769,7 +20775,7 @@
       <c r="C42" s="9" t="s">
         <v>2207</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="19" t="s">
         <v>2208</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -20777,7 +20783,7 @@
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="18" t="s">
         <v>2209</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -20786,7 +20792,7 @@
       <c r="C43" s="9" t="s">
         <v>2211</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="19" t="s">
         <v>2212</v>
       </c>
       <c r="E43" s="12" t="s">
@@ -20794,7 +20800,7 @@
       </c>
     </row>
     <row r="44" ht="31" customHeight="1">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="18" t="s">
         <v>2213</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -20803,7 +20809,7 @@
       <c r="C44" s="9" t="s">
         <v>2215</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="19" t="s">
         <v>2216</v>
       </c>
       <c r="E44" s="12" t="s">
@@ -20811,7 +20817,7 @@
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="18" t="s">
         <v>2217</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -20820,7 +20826,7 @@
       <c r="C45" s="9" t="s">
         <v>2219</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="19" t="s">
         <v>2220</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -20828,7 +20834,7 @@
       </c>
     </row>
     <row r="46" ht="31" customHeight="1">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="18" t="s">
         <v>2221</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -20837,7 +20843,7 @@
       <c r="C46" s="9" t="s">
         <v>2223</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="19" t="s">
         <v>2224</v>
       </c>
       <c r="E46" s="12" t="s">
@@ -20845,7 +20851,7 @@
       </c>
     </row>
     <row r="47" ht="31" customHeight="1">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="18" t="s">
         <v>2225</v>
       </c>
       <c r="B47" s="8" t="s">
@@ -20854,7 +20860,7 @@
       <c r="C47" s="9" t="s">
         <v>2227</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="19" t="s">
         <v>2228</v>
       </c>
       <c r="E47" s="12" t="s">
@@ -20862,7 +20868,7 @@
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="18" t="s">
         <v>2229</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -20871,7 +20877,7 @@
       <c r="C48" s="9" t="s">
         <v>2231</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="19" t="s">
         <v>2232</v>
       </c>
       <c r="E48" s="12" t="s">
@@ -20879,7 +20885,7 @@
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="18" t="s">
         <v>2233</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -20888,7 +20894,7 @@
       <c r="C49" s="9" t="s">
         <v>2235</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="19" t="s">
         <v>2236</v>
       </c>
       <c r="E49" s="13" t="s">
@@ -20896,7 +20902,7 @@
       </c>
     </row>
     <row r="50" ht="31" customHeight="1">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="18" t="s">
         <v>2237</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -20905,7 +20911,7 @@
       <c r="C50" s="9" t="s">
         <v>2239</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="19" t="s">
         <v>2240</v>
       </c>
       <c r="E50" s="13" t="s">
@@ -20913,7 +20919,7 @@
       </c>
     </row>
     <row r="51" ht="31" customHeight="1">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="18" t="s">
         <v>2241</v>
       </c>
       <c r="B51" s="8" t="s">
@@ -20922,7 +20928,7 @@
       <c r="C51" s="9" t="s">
         <v>2243</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="19" t="s">
         <v>2244</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -20930,7 +20936,7 @@
       </c>
     </row>
     <row r="52" ht="31" customHeight="1">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="18" t="s">
         <v>2245</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -20939,7 +20945,7 @@
       <c r="C52" s="9" t="s">
         <v>2247</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="19" t="s">
         <v>2248</v>
       </c>
       <c r="E52" s="13" t="s">
@@ -20947,7 +20953,7 @@
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="18" t="s">
         <v>2249</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -20956,7 +20962,7 @@
       <c r="C53" s="9" t="s">
         <v>2251</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="19" t="s">
         <v>2252</v>
       </c>
       <c r="E53" s="13" t="s">
@@ -20964,7 +20970,7 @@
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="18" t="s">
         <v>2253</v>
       </c>
       <c r="B54" s="8" t="s">
@@ -20973,7 +20979,7 @@
       <c r="C54" s="9" t="s">
         <v>2255</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D54" s="19" t="s">
         <v>2256</v>
       </c>
       <c r="E54" s="13" t="s">
@@ -20981,7 +20987,7 @@
       </c>
     </row>
     <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="18" t="s">
         <v>2257</v>
       </c>
       <c r="B55" s="8" t="s">
@@ -20990,7 +20996,7 @@
       <c r="C55" s="9" t="s">
         <v>2259</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D55" s="19" t="s">
         <v>2260</v>
       </c>
       <c r="E55" s="13" t="s">
@@ -20998,7 +21004,7 @@
       </c>
     </row>
     <row r="56" ht="26" customHeight="1">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="18" t="s">
         <v>2261</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -21007,7 +21013,7 @@
       <c r="C56" s="9" t="s">
         <v>2263</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="19" t="s">
         <v>2264</v>
       </c>
       <c r="E56" s="13" t="s">
@@ -21015,7 +21021,7 @@
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="18" t="s">
         <v>2265</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -21024,7 +21030,7 @@
       <c r="C57" s="9" t="s">
         <v>2267</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="19" t="s">
         <v>2268</v>
       </c>
       <c r="E57" s="13" t="s">
@@ -21032,7 +21038,7 @@
       </c>
     </row>
     <row r="58" ht="26" customHeight="1">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="18" t="s">
         <v>2269</v>
       </c>
       <c r="B58" s="8" t="s">
@@ -21041,7 +21047,7 @@
       <c r="C58" s="9" t="s">
         <v>2271</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="19" t="s">
         <v>2272</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -21049,7 +21055,7 @@
       </c>
     </row>
     <row r="59" ht="31" customHeight="1">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="18" t="s">
         <v>2273</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -21058,7 +21064,7 @@
       <c r="C59" s="9" t="s">
         <v>2275</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="D59" s="19" t="s">
         <v>2276</v>
       </c>
       <c r="E59" s="13" t="s">
@@ -21066,7 +21072,7 @@
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="18" t="s">
         <v>2277</v>
       </c>
       <c r="B60" s="8" t="s">
@@ -21075,7 +21081,7 @@
       <c r="C60" s="9" t="s">
         <v>2279</v>
       </c>
-      <c r="D60" s="18" t="s">
+      <c r="D60" s="19" t="s">
         <v>2280</v>
       </c>
       <c r="E60" s="13" t="s">
@@ -21127,7 +21133,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>2282</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -21136,7 +21142,7 @@
       <c r="C2" s="9" t="s">
         <v>2284</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>2285</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -21144,7 +21150,7 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>2286</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -21153,7 +21159,7 @@
       <c r="C3" s="9" t="s">
         <v>2288</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>1317</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -21161,7 +21167,7 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>2289</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -21170,7 +21176,7 @@
       <c r="C4" s="9" t="s">
         <v>2291</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>2292</v>
       </c>
       <c r="E4" s="11" t="s">
@@ -21178,7 +21184,7 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>2293</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -21187,7 +21193,7 @@
       <c r="C5" s="9" t="s">
         <v>2295</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>2296</v>
       </c>
       <c r="E5" s="11" t="s">
@@ -21195,7 +21201,7 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>2297</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -21204,7 +21210,7 @@
       <c r="C6" s="9" t="s">
         <v>2299</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>2300</v>
       </c>
       <c r="E6" s="11" t="s">
@@ -21212,7 +21218,7 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>2301</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -21221,7 +21227,7 @@
       <c r="C7" s="9" t="s">
         <v>2303</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>1243</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -21229,7 +21235,7 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>2304</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -21238,7 +21244,7 @@
       <c r="C8" s="9" t="s">
         <v>2306</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>2307</v>
       </c>
       <c r="E8" s="11" t="s">
@@ -21246,7 +21252,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>2308</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -21255,7 +21261,7 @@
       <c r="C9" s="9" t="s">
         <v>2310</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>2311</v>
       </c>
       <c r="E9" s="11" t="s">
@@ -21263,7 +21269,7 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>2312</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -21272,7 +21278,7 @@
       <c r="C10" s="9" t="s">
         <v>2314</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>2315</v>
       </c>
       <c r="E10" s="11" t="s">
@@ -21280,7 +21286,7 @@
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>2316</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -21289,7 +21295,7 @@
       <c r="C11" s="9" t="s">
         <v>2318</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>2319</v>
       </c>
       <c r="E11" s="11" t="s">
@@ -21297,7 +21303,7 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>2320</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -21306,7 +21312,7 @@
       <c r="C12" s="9" t="s">
         <v>2322</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>2323</v>
       </c>
       <c r="E12" s="11" t="s">
@@ -21314,7 +21320,7 @@
       </c>
     </row>
     <row r="13" ht="31" customHeight="1">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>2324</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -21323,7 +21329,7 @@
       <c r="C13" s="9" t="s">
         <v>2326</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>2327</v>
       </c>
       <c r="E13" s="11" t="s">
@@ -21331,7 +21337,7 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>2328</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -21340,7 +21346,7 @@
       <c r="C14" s="9" t="s">
         <v>2330</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>2331</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -21348,7 +21354,7 @@
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>2332</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -21357,7 +21363,7 @@
       <c r="C15" s="9" t="s">
         <v>2334</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>2335</v>
       </c>
       <c r="E15" s="11" t="s">
@@ -21365,7 +21371,7 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>2336</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -21374,7 +21380,7 @@
       <c r="C16" s="9" t="s">
         <v>2338</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>2339</v>
       </c>
       <c r="E16" s="11" t="s">
@@ -21382,7 +21388,7 @@
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>2340</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -21391,7 +21397,7 @@
       <c r="C17" s="9" t="s">
         <v>2342</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>2343</v>
       </c>
       <c r="E17" s="11" t="s">
@@ -21399,7 +21405,7 @@
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>2344</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -21408,7 +21414,7 @@
       <c r="C18" s="9" t="s">
         <v>2346</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>2347</v>
       </c>
       <c r="E18" s="11" t="s">
@@ -21416,7 +21422,7 @@
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>2348</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -21425,7 +21431,7 @@
       <c r="C19" s="9" t="s">
         <v>2350</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>2351</v>
       </c>
       <c r="E19" s="11" t="s">
@@ -21433,7 +21439,7 @@
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>2352</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -21442,7 +21448,7 @@
       <c r="C20" s="9" t="s">
         <v>2354</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>1392</v>
       </c>
       <c r="E20" s="11" t="s">
@@ -21450,7 +21456,7 @@
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>2355</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -21459,7 +21465,7 @@
       <c r="C21" s="9" t="s">
         <v>2357</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>2358</v>
       </c>
       <c r="E21" s="11" t="s">
@@ -21467,7 +21473,7 @@
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>2359</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -21476,7 +21482,7 @@
       <c r="C22" s="9" t="s">
         <v>2361</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>2362</v>
       </c>
       <c r="E22" s="11" t="s">
@@ -21484,7 +21490,7 @@
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>2363</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -21493,7 +21499,7 @@
       <c r="C23" s="9" t="s">
         <v>2365</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="19" t="s">
         <v>2366</v>
       </c>
       <c r="E23" s="11" t="s">
@@ -21501,7 +21507,7 @@
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>2367</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -21510,7 +21516,7 @@
       <c r="C24" s="9" t="s">
         <v>2369</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="19" t="s">
         <v>2370</v>
       </c>
       <c r="E24" s="11" t="s">
@@ -21518,7 +21524,7 @@
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>2371</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -21527,7 +21533,7 @@
       <c r="C25" s="9" t="s">
         <v>2373</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="19" t="s">
         <v>2374</v>
       </c>
       <c r="E25" s="11" t="s">
@@ -21535,7 +21541,7 @@
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>2375</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -21544,7 +21550,7 @@
       <c r="C26" s="9" t="s">
         <v>2377</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="19" t="s">
         <v>2378</v>
       </c>
       <c r="E26" s="11" t="s">
@@ -21552,7 +21558,7 @@
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>2379</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -21561,7 +21567,7 @@
       <c r="C27" s="9" t="s">
         <v>2381</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="19" t="s">
         <v>2382</v>
       </c>
       <c r="E27" s="11" t="s">
@@ -21569,7 +21575,7 @@
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>2383</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -21578,7 +21584,7 @@
       <c r="C28" s="9" t="s">
         <v>2385</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="19" t="s">
         <v>2386</v>
       </c>
       <c r="E28" s="11" t="s">
@@ -21586,7 +21592,7 @@
       </c>
     </row>
     <row r="29" ht="31" customHeight="1">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>2387</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -21595,7 +21601,7 @@
       <c r="C29" s="9" t="s">
         <v>2389</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="19" t="s">
         <v>2390</v>
       </c>
       <c r="E29" s="11" t="s">
@@ -21603,7 +21609,7 @@
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>2391</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -21612,7 +21618,7 @@
       <c r="C30" s="9" t="s">
         <v>2393</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="19" t="s">
         <v>2394</v>
       </c>
       <c r="E30" s="11" t="s">
@@ -21620,7 +21626,7 @@
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>2395</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -21629,7 +21635,7 @@
       <c r="C31" s="9" t="s">
         <v>2397</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="19" t="s">
         <v>2398</v>
       </c>
       <c r="E31" s="11" t="s">
@@ -21637,7 +21643,7 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
         <v>2399</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -21646,7 +21652,7 @@
       <c r="C32" s="9" t="s">
         <v>2401</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="19" t="s">
         <v>2402</v>
       </c>
       <c r="E32" s="11" t="s">
@@ -21654,7 +21660,7 @@
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>2403</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -21663,7 +21669,7 @@
       <c r="C33" s="9" t="s">
         <v>2405</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="19" t="s">
         <v>2406</v>
       </c>
       <c r="E33" s="11" t="s">
@@ -21671,7 +21677,7 @@
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
         <v>2407</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -21680,7 +21686,7 @@
       <c r="C34" s="9" t="s">
         <v>2409</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="19" t="s">
         <v>1339</v>
       </c>
       <c r="E34" s="11" t="s">
@@ -21688,7 +21694,7 @@
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>2410</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -21697,7 +21703,7 @@
       <c r="C35" s="9" t="s">
         <v>2412</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="19" t="s">
         <v>2413</v>
       </c>
       <c r="E35" s="12" t="s">
@@ -21705,7 +21711,7 @@
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="18" t="s">
         <v>2414</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -21714,7 +21720,7 @@
       <c r="C36" s="9" t="s">
         <v>2416</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="19" t="s">
         <v>2417</v>
       </c>
       <c r="E36" s="12" t="s">
@@ -21722,7 +21728,7 @@
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="18" t="s">
         <v>2418</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -21731,7 +21737,7 @@
       <c r="C37" s="9" t="s">
         <v>2420</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="19" t="s">
         <v>2421</v>
       </c>
       <c r="E37" s="12" t="s">
@@ -21739,7 +21745,7 @@
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>2422</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -21748,7 +21754,7 @@
       <c r="C38" s="9" t="s">
         <v>2424</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="19" t="s">
         <v>2425</v>
       </c>
       <c r="E38" s="12" t="s">
@@ -21756,7 +21762,7 @@
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="18" t="s">
         <v>2426</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -21765,7 +21771,7 @@
       <c r="C39" s="9" t="s">
         <v>2428</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="19" t="s">
         <v>2429</v>
       </c>
       <c r="E39" s="12" t="s">
@@ -21773,7 +21779,7 @@
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="18" t="s">
         <v>2430</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -21782,7 +21788,7 @@
       <c r="C40" s="9" t="s">
         <v>2432</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="19" t="s">
         <v>2433</v>
       </c>
       <c r="E40" s="12" t="s">
@@ -21790,7 +21796,7 @@
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>2434</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -21799,7 +21805,7 @@
       <c r="C41" s="9" t="s">
         <v>2436</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="19" t="s">
         <v>2437</v>
       </c>
       <c r="E41" s="12" t="s">
@@ -21807,7 +21813,7 @@
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="18" t="s">
         <v>2438</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -21816,7 +21822,7 @@
       <c r="C42" s="9" t="s">
         <v>2440</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="19" t="s">
         <v>2441</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -21824,7 +21830,7 @@
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="18" t="s">
         <v>2442</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -21833,7 +21839,7 @@
       <c r="C43" s="9" t="s">
         <v>2444</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="19" t="s">
         <v>2445</v>
       </c>
       <c r="E43" s="12" t="s">
@@ -21841,7 +21847,7 @@
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="18" t="s">
         <v>2446</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -21850,7 +21856,7 @@
       <c r="C44" s="9" t="s">
         <v>2448</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="19" t="s">
         <v>2449</v>
       </c>
       <c r="E44" s="12" t="s">
@@ -21858,7 +21864,7 @@
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="18" t="s">
         <v>2450</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -21867,7 +21873,7 @@
       <c r="C45" s="9" t="s">
         <v>2452</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="19" t="s">
         <v>1137</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -21875,7 +21881,7 @@
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="18" t="s">
         <v>2453</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -21884,7 +21890,7 @@
       <c r="C46" s="9" t="s">
         <v>2455</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="19" t="s">
         <v>2456</v>
       </c>
       <c r="E46" s="12" t="s">
@@ -21892,7 +21898,7 @@
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="18" t="s">
         <v>2457</v>
       </c>
       <c r="B47" s="8" t="s">
@@ -21901,7 +21907,7 @@
       <c r="C47" s="9" t="s">
         <v>2459</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="19" t="s">
         <v>2460</v>
       </c>
       <c r="E47" s="12" t="s">
@@ -21909,7 +21915,7 @@
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="18" t="s">
         <v>2461</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -21918,7 +21924,7 @@
       <c r="C48" s="9" t="s">
         <v>2463</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="19" t="s">
         <v>2464</v>
       </c>
       <c r="E48" s="12" t="s">
@@ -21926,7 +21932,7 @@
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="18" t="s">
         <v>2465</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -21935,7 +21941,7 @@
       <c r="C49" s="9" t="s">
         <v>2467</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="19" t="s">
         <v>2468</v>
       </c>
       <c r="E49" s="12" t="s">
@@ -21943,7 +21949,7 @@
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="18" t="s">
         <v>2469</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -21952,7 +21958,7 @@
       <c r="C50" s="9" t="s">
         <v>2471</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="19" t="s">
         <v>2472</v>
       </c>
       <c r="E50" s="12" t="s">
@@ -21960,7 +21966,7 @@
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="18" t="s">
         <v>2473</v>
       </c>
       <c r="B51" s="8" t="s">
@@ -21969,7 +21975,7 @@
       <c r="C51" s="9" t="s">
         <v>2475</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="19" t="s">
         <v>2476</v>
       </c>
       <c r="E51" s="12" t="s">
@@ -21977,7 +21983,7 @@
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="18" t="s">
         <v>2477</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -21986,7 +21992,7 @@
       <c r="C52" s="9" t="s">
         <v>2479</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="19" t="s">
         <v>2480</v>
       </c>
       <c r="E52" s="12" t="s">
@@ -21994,7 +22000,7 @@
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="18" t="s">
         <v>2481</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -22003,7 +22009,7 @@
       <c r="C53" s="9" t="s">
         <v>2483</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="19" t="s">
         <v>2484</v>
       </c>
       <c r="E53" s="12" t="s">
@@ -22011,7 +22017,7 @@
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="18" t="s">
         <v>2485</v>
       </c>
       <c r="B54" s="8" t="s">
@@ -22020,7 +22026,7 @@
       <c r="C54" s="9" t="s">
         <v>2487</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D54" s="19" t="s">
         <v>2488</v>
       </c>
       <c r="E54" s="12" t="s">
@@ -22028,7 +22034,7 @@
       </c>
     </row>
     <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="18" t="s">
         <v>2489</v>
       </c>
       <c r="B55" s="8" t="s">
@@ -22037,7 +22043,7 @@
       <c r="C55" s="9" t="s">
         <v>2491</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D55" s="19" t="s">
         <v>2492</v>
       </c>
       <c r="E55" s="12" t="s">
@@ -22045,7 +22051,7 @@
       </c>
     </row>
     <row r="56" ht="26" customHeight="1">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="18" t="s">
         <v>2493</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -22054,7 +22060,7 @@
       <c r="C56" s="9" t="s">
         <v>2495</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="19" t="s">
         <v>2496</v>
       </c>
       <c r="E56" s="12" t="s">
@@ -22062,7 +22068,7 @@
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="18" t="s">
         <v>2497</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -22071,7 +22077,7 @@
       <c r="C57" s="9" t="s">
         <v>2499</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="19" t="s">
         <v>2500</v>
       </c>
       <c r="E57" s="12" t="s">
@@ -22079,7 +22085,7 @@
       </c>
     </row>
     <row r="58" ht="26" customHeight="1">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="18" t="s">
         <v>2501</v>
       </c>
       <c r="B58" s="8" t="s">
@@ -22088,7 +22094,7 @@
       <c r="C58" s="9" t="s">
         <v>2503</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="19" t="s">
         <v>2504</v>
       </c>
       <c r="E58" s="12" t="s">
@@ -22096,7 +22102,7 @@
       </c>
     </row>
     <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="18" t="s">
         <v>2505</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -22105,7 +22111,7 @@
       <c r="C59" s="9" t="s">
         <v>2507</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="D59" s="19" t="s">
         <v>2508</v>
       </c>
       <c r="E59" s="12" t="s">
@@ -22113,7 +22119,7 @@
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="18" t="s">
         <v>2509</v>
       </c>
       <c r="B60" s="8" t="s">
@@ -22122,7 +22128,7 @@
       <c r="C60" s="9" t="s">
         <v>2511</v>
       </c>
-      <c r="D60" s="18" t="s">
+      <c r="D60" s="19" t="s">
         <v>2512</v>
       </c>
       <c r="E60" s="12" t="s">
@@ -22130,7 +22136,7 @@
       </c>
     </row>
     <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="17" t="s">
+      <c r="A61" s="18" t="s">
         <v>2513</v>
       </c>
       <c r="B61" s="8" t="s">
@@ -22139,7 +22145,7 @@
       <c r="C61" s="9" t="s">
         <v>2515</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="D61" s="19" t="s">
         <v>2516</v>
       </c>
       <c r="E61" s="12" t="s">
@@ -22147,7 +22153,7 @@
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="18" t="s">
         <v>2517</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -22156,7 +22162,7 @@
       <c r="C62" s="9" t="s">
         <v>2519</v>
       </c>
-      <c r="D62" s="18" t="s">
+      <c r="D62" s="19" t="s">
         <v>2520</v>
       </c>
       <c r="E62" s="12" t="s">
@@ -22164,7 +22170,7 @@
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="18" t="s">
         <v>2521</v>
       </c>
       <c r="B63" s="8" t="s">
@@ -22173,7 +22179,7 @@
       <c r="C63" s="9" t="s">
         <v>2523</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="D63" s="19" t="s">
         <v>2524</v>
       </c>
       <c r="E63" s="12" t="s">
@@ -22181,7 +22187,7 @@
       </c>
     </row>
     <row r="64" ht="26" customHeight="1">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="18" t="s">
         <v>2525</v>
       </c>
       <c r="B64" s="8" t="s">
@@ -22190,7 +22196,7 @@
       <c r="C64" s="9" t="s">
         <v>2527</v>
       </c>
-      <c r="D64" s="18" t="s">
+      <c r="D64" s="19" t="s">
         <v>2528</v>
       </c>
       <c r="E64" s="12" t="s">
@@ -22198,7 +22204,7 @@
       </c>
     </row>
     <row r="65" ht="31" customHeight="1">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="18" t="s">
         <v>2529</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -22207,7 +22213,7 @@
       <c r="C65" s="9" t="s">
         <v>2531</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="D65" s="19" t="s">
         <v>2532</v>
       </c>
       <c r="E65" s="12" t="s">
@@ -22215,7 +22221,7 @@
       </c>
     </row>
     <row r="66" ht="26" customHeight="1">
-      <c r="A66" s="17" t="s">
+      <c r="A66" s="18" t="s">
         <v>2533</v>
       </c>
       <c r="B66" s="8" t="s">
@@ -22224,7 +22230,7 @@
       <c r="C66" s="9" t="s">
         <v>2535</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="D66" s="19" t="s">
         <v>2536</v>
       </c>
       <c r="E66" s="12" t="s">
@@ -22232,7 +22238,7 @@
       </c>
     </row>
     <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="17" t="s">
+      <c r="A67" s="18" t="s">
         <v>2537</v>
       </c>
       <c r="B67" s="8" t="s">
@@ -22241,7 +22247,7 @@
       <c r="C67" s="9" t="s">
         <v>2539</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="D67" s="19" t="s">
         <v>2540</v>
       </c>
       <c r="E67" s="12" t="s">
@@ -22249,7 +22255,7 @@
       </c>
     </row>
     <row r="68" ht="26" customHeight="1">
-      <c r="A68" s="17" t="s">
+      <c r="A68" s="18" t="s">
         <v>2541</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -22258,7 +22264,7 @@
       <c r="C68" s="9" t="s">
         <v>2543</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="D68" s="19" t="s">
         <v>2544</v>
       </c>
       <c r="E68" s="12" t="s">
@@ -22266,7 +22272,7 @@
       </c>
     </row>
     <row r="69" ht="26" customHeight="1">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="18" t="s">
         <v>2545</v>
       </c>
       <c r="B69" s="8" t="s">
@@ -22275,7 +22281,7 @@
       <c r="C69" s="9" t="s">
         <v>2547</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="D69" s="19" t="s">
         <v>2548</v>
       </c>
       <c r="E69" s="12" t="s">
@@ -22283,7 +22289,7 @@
       </c>
     </row>
     <row r="70" ht="26" customHeight="1">
-      <c r="A70" s="17" t="s">
+      <c r="A70" s="18" t="s">
         <v>2549</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -22292,7 +22298,7 @@
       <c r="C70" s="9" t="s">
         <v>2551</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="D70" s="19" t="s">
         <v>2552</v>
       </c>
       <c r="E70" s="12" t="s">
@@ -22300,7 +22306,7 @@
       </c>
     </row>
     <row r="71" ht="31" customHeight="1">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="18" t="s">
         <v>2553</v>
       </c>
       <c r="B71" s="8" t="s">
@@ -22309,7 +22315,7 @@
       <c r="C71" s="9" t="s">
         <v>2555</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D71" s="19" t="s">
         <v>2556</v>
       </c>
       <c r="E71" s="13" t="s">
@@ -22361,7 +22367,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>2558</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -22370,7 +22376,7 @@
       <c r="C2" s="9" t="s">
         <v>2560</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>910</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -22378,7 +22384,7 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>2561</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -22387,7 +22393,7 @@
       <c r="C3" s="9" t="s">
         <v>2563</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>2564</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -22395,7 +22401,7 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>2565</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -22404,7 +22410,7 @@
       <c r="C4" s="9" t="s">
         <v>2567</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>2568</v>
       </c>
       <c r="E4" s="11" t="s">
@@ -22412,7 +22418,7 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>2569</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -22421,7 +22427,7 @@
       <c r="C5" s="9" t="s">
         <v>2571</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>1240</v>
       </c>
       <c r="E5" s="11" t="s">
@@ -22429,7 +22435,7 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>2572</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -22438,7 +22444,7 @@
       <c r="C6" s="9" t="s">
         <v>2574</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>2575</v>
       </c>
       <c r="E6" s="11" t="s">
@@ -22446,7 +22452,7 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>2576</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -22455,7 +22461,7 @@
       <c r="C7" s="9" t="s">
         <v>2578</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>2579</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -22463,7 +22469,7 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>2580</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -22472,7 +22478,7 @@
       <c r="C8" s="9" t="s">
         <v>2582</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>2583</v>
       </c>
       <c r="E8" s="11" t="s">
@@ -22480,7 +22486,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>2584</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -22489,7 +22495,7 @@
       <c r="C9" s="9" t="s">
         <v>2586</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>2587</v>
       </c>
       <c r="E9" s="12" t="s">
@@ -22497,7 +22503,7 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>2588</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -22506,7 +22512,7 @@
       <c r="C10" s="9" t="s">
         <v>2590</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>2591</v>
       </c>
       <c r="E10" s="12" t="s">
@@ -22514,7 +22520,7 @@
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>2592</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -22523,7 +22529,7 @@
       <c r="C11" s="9" t="s">
         <v>2594</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>2595</v>
       </c>
       <c r="E11" s="12" t="s">
@@ -22531,7 +22537,7 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>2596</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -22540,7 +22546,7 @@
       <c r="C12" s="9" t="s">
         <v>2598</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>2599</v>
       </c>
       <c r="E12" s="12" t="s">
@@ -22548,7 +22554,7 @@
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>2600</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -22557,7 +22563,7 @@
       <c r="C13" s="9" t="s">
         <v>2602</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>2603</v>
       </c>
       <c r="E13" s="12" t="s">
@@ -22565,7 +22571,7 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>2604</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -22574,7 +22580,7 @@
       <c r="C14" s="9" t="s">
         <v>2606</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>2607</v>
       </c>
       <c r="E14" s="12" t="s">
@@ -22582,7 +22588,7 @@
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>2608</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -22591,7 +22597,7 @@
       <c r="C15" s="9" t="s">
         <v>2610</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>2611</v>
       </c>
       <c r="E15" s="12" t="s">
@@ -22599,7 +22605,7 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>2612</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -22608,7 +22614,7 @@
       <c r="C16" s="9" t="s">
         <v>2614</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>2615</v>
       </c>
       <c r="E16" s="12" t="s">
@@ -22616,7 +22622,7 @@
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>2616</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -22625,7 +22631,7 @@
       <c r="C17" s="9" t="s">
         <v>2618</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>1334</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -22633,7 +22639,7 @@
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>2619</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -22642,7 +22648,7 @@
       <c r="C18" s="9" t="s">
         <v>2621</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>2622</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -22650,7 +22656,7 @@
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>2623</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -22659,7 +22665,7 @@
       <c r="C19" s="9" t="s">
         <v>2625</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>2626</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -22667,7 +22673,7 @@
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>2627</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -22676,7 +22682,7 @@
       <c r="C20" s="9" t="s">
         <v>2629</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>2630</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -22684,7 +22690,7 @@
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>2631</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -22693,7 +22699,7 @@
       <c r="C21" s="9" t="s">
         <v>2633</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>2634</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -22701,7 +22707,7 @@
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>2635</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -22710,7 +22716,7 @@
       <c r="C22" s="9" t="s">
         <v>2637</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>2638</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -22718,7 +22724,7 @@
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>2639</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -22727,7 +22733,7 @@
       <c r="C23" s="9" t="s">
         <v>2641</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="19" t="s">
         <v>2642</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -22735,7 +22741,7 @@
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>2643</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -22744,7 +22750,7 @@
       <c r="C24" s="9" t="s">
         <v>2645</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="19" t="s">
         <v>2646</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -22752,7 +22758,7 @@
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>2647</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -22761,7 +22767,7 @@
       <c r="C25" s="9" t="s">
         <v>2649</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="19" t="s">
         <v>2650</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -22769,7 +22775,7 @@
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>2651</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -22778,7 +22784,7 @@
       <c r="C26" s="9" t="s">
         <v>2653</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="19" t="s">
         <v>2654</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -22786,7 +22792,7 @@
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>2655</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -22795,7 +22801,7 @@
       <c r="C27" s="9" t="s">
         <v>2657</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="19" t="s">
         <v>2658</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -22803,7 +22809,7 @@
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>2659</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -22812,7 +22818,7 @@
       <c r="C28" s="9" t="s">
         <v>2661</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="19" t="s">
         <v>2662</v>
       </c>
       <c r="E28" s="12" t="s">
@@ -22820,7 +22826,7 @@
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>2663</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -22829,7 +22835,7 @@
       <c r="C29" s="9" t="s">
         <v>2665</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="19" t="s">
         <v>2666</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -22837,7 +22843,7 @@
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>2667</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -22846,7 +22852,7 @@
       <c r="C30" s="9" t="s">
         <v>2669</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="19" t="s">
         <v>2670</v>
       </c>
       <c r="E30" s="13" t="s">
@@ -22854,7 +22860,7 @@
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>2671</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -22863,7 +22869,7 @@
       <c r="C31" s="9" t="s">
         <v>2673</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="19" t="s">
         <v>2674</v>
       </c>
       <c r="E31" s="13" t="s">
@@ -22871,7 +22877,7 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
         <v>2675</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -22880,7 +22886,7 @@
       <c r="C32" s="9" t="s">
         <v>2677</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="19" t="s">
         <v>2678</v>
       </c>
       <c r="E32" s="13" t="s">
@@ -22888,7 +22894,7 @@
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>2679</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -22897,7 +22903,7 @@
       <c r="C33" s="9" t="s">
         <v>2681</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="19" t="s">
         <v>2682</v>
       </c>
       <c r="E33" s="13" t="s">
@@ -22905,7 +22911,7 @@
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
         <v>2683</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -22914,7 +22920,7 @@
       <c r="C34" s="9" t="s">
         <v>2685</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="19" t="s">
         <v>2686</v>
       </c>
       <c r="E34" s="13" t="s">
@@ -22922,7 +22928,7 @@
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>2687</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -22931,7 +22937,7 @@
       <c r="C35" s="9" t="s">
         <v>2689</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="19" t="s">
         <v>2690</v>
       </c>
       <c r="E35" s="13" t="s">
@@ -22939,7 +22945,7 @@
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="18" t="s">
         <v>2691</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -22948,7 +22954,7 @@
       <c r="C36" s="9" t="s">
         <v>2693</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="19" t="s">
         <v>2694</v>
       </c>
       <c r="E36" s="13" t="s">
@@ -22956,7 +22962,7 @@
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="18" t="s">
         <v>2695</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -22965,7 +22971,7 @@
       <c r="C37" s="9" t="s">
         <v>2697</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="19" t="s">
         <v>2698</v>
       </c>
       <c r="E37" s="13" t="s">
@@ -22973,7 +22979,7 @@
       </c>
     </row>
     <row r="38" ht="31" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>2699</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -22982,7 +22988,7 @@
       <c r="C38" s="9" t="s">
         <v>2701</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="19" t="s">
         <v>2702</v>
       </c>
       <c r="E38" s="13" t="s">
@@ -22990,7 +22996,7 @@
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="18" t="s">
         <v>2703</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -22999,7 +23005,7 @@
       <c r="C39" s="9" t="s">
         <v>2705</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="19" t="s">
         <v>2706</v>
       </c>
       <c r="E39" s="13" t="s">
@@ -23007,7 +23013,7 @@
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="18" t="s">
         <v>2707</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -23016,7 +23022,7 @@
       <c r="C40" s="9" t="s">
         <v>2709</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="19" t="s">
         <v>2710</v>
       </c>
       <c r="E40" s="13" t="s">
@@ -23024,7 +23030,7 @@
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>2711</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -23033,7 +23039,7 @@
       <c r="C41" s="9" t="s">
         <v>2713</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="19" t="s">
         <v>2714</v>
       </c>
       <c r="E41" s="13" t="s">
@@ -23041,7 +23047,7 @@
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="18" t="s">
         <v>2715</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -23050,7 +23056,7 @@
       <c r="C42" s="9" t="s">
         <v>2717</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="19" t="s">
         <v>2718</v>
       </c>
       <c r="E42" s="13" t="s">
@@ -23058,7 +23064,7 @@
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="18" t="s">
         <v>2719</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -23067,7 +23073,7 @@
       <c r="C43" s="9" t="s">
         <v>2721</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="19" t="s">
         <v>2722</v>
       </c>
       <c r="E43" s="13" t="s">
@@ -23075,7 +23081,7 @@
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="18" t="s">
         <v>2723</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -23084,7 +23090,7 @@
       <c r="C44" s="9" t="s">
         <v>2725</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="19" t="s">
         <v>2726</v>
       </c>
       <c r="E44" s="13" t="s">
@@ -23092,7 +23098,7 @@
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="18" t="s">
         <v>2727</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -23101,7 +23107,7 @@
       <c r="C45" s="9" t="s">
         <v>2729</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="19" t="s">
         <v>2730</v>
       </c>
       <c r="E45" s="13" t="s">
@@ -23153,7 +23159,7 @@
       </c>
     </row>
     <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>2732</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -23162,7 +23168,7 @@
       <c r="C2" s="9" t="s">
         <v>2734</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>2735</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -23170,7 +23176,7 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>2736</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -23179,7 +23185,7 @@
       <c r="C3" s="9" t="s">
         <v>2738</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>2739</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -23187,7 +23193,7 @@
       </c>
     </row>
     <row r="4" ht="31" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>2740</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -23196,7 +23202,7 @@
       <c r="C4" s="9" t="s">
         <v>2742</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>2743</v>
       </c>
       <c r="E4" s="11" t="s">
@@ -23204,7 +23210,7 @@
       </c>
     </row>
     <row r="5" ht="31" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>2744</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -23213,7 +23219,7 @@
       <c r="C5" s="9" t="s">
         <v>2746</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>2747</v>
       </c>
       <c r="E5" s="12" t="s">
@@ -23221,7 +23227,7 @@
       </c>
     </row>
     <row r="6" ht="31" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>2748</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -23230,7 +23236,7 @@
       <c r="C6" s="9" t="s">
         <v>2750</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>2751</v>
       </c>
       <c r="E6" s="12" t="s">
@@ -23238,7 +23244,7 @@
       </c>
     </row>
     <row r="7" ht="31" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>2752</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -23247,7 +23253,7 @@
       <c r="C7" s="9" t="s">
         <v>2754</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>2755</v>
       </c>
       <c r="E7" s="12" t="s">
@@ -23255,7 +23261,7 @@
       </c>
     </row>
     <row r="8" ht="31" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>2756</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -23264,7 +23270,7 @@
       <c r="C8" s="9" t="s">
         <v>2758</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>2759</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -23272,7 +23278,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>2760</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -23281,7 +23287,7 @@
       <c r="C9" s="9" t="s">
         <v>2762</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>2763</v>
       </c>
       <c r="E9" s="12" t="s">
@@ -23289,7 +23295,7 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>2764</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -23298,7 +23304,7 @@
       <c r="C10" s="9" t="s">
         <v>2766</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>2767</v>
       </c>
       <c r="E10" s="12" t="s">
@@ -23306,7 +23312,7 @@
       </c>
     </row>
     <row r="11" ht="31" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>2768</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -23315,7 +23321,7 @@
       <c r="C11" s="9" t="s">
         <v>2770</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>2771</v>
       </c>
       <c r="E11" s="12" t="s">
@@ -23323,7 +23329,7 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>2772</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -23332,7 +23338,7 @@
       <c r="C12" s="9" t="s">
         <v>2774</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>2775</v>
       </c>
       <c r="E12" s="12" t="s">
@@ -23340,7 +23346,7 @@
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>2776</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -23349,7 +23355,7 @@
       <c r="C13" s="9" t="s">
         <v>2778</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>2779</v>
       </c>
       <c r="E13" s="12" t="s">
@@ -23357,7 +23363,7 @@
       </c>
     </row>
     <row r="14" ht="31" customHeight="1">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>2780</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -23366,7 +23372,7 @@
       <c r="C14" s="9" t="s">
         <v>2782</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>2783</v>
       </c>
       <c r="E14" s="12" t="s">
@@ -23374,7 +23380,7 @@
       </c>
     </row>
     <row r="15" ht="31" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>2784</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -23383,7 +23389,7 @@
       <c r="C15" s="9" t="s">
         <v>2786</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>2787</v>
       </c>
       <c r="E15" s="12" t="s">
@@ -23391,7 +23397,7 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>2788</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -23400,7 +23406,7 @@
       <c r="C16" s="9" t="s">
         <v>2790</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>731</v>
       </c>
       <c r="E16" s="12" t="s">
@@ -23408,7 +23414,7 @@
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>2791</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -23417,7 +23423,7 @@
       <c r="C17" s="9" t="s">
         <v>2793</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>2794</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -23425,7 +23431,7 @@
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>2795</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -23434,7 +23440,7 @@
       <c r="C18" s="9" t="s">
         <v>2797</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>2798</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -23442,7 +23448,7 @@
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>2799</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -23451,7 +23457,7 @@
       <c r="C19" s="9" t="s">
         <v>2801</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>2802</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -23459,7 +23465,7 @@
       </c>
     </row>
     <row r="20" ht="31" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>2803</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -23468,7 +23474,7 @@
       <c r="C20" s="9" t="s">
         <v>2805</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>2806</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -23476,7 +23482,7 @@
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>2807</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -23485,7 +23491,7 @@
       <c r="C21" s="9" t="s">
         <v>2809</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>2810</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -23493,7 +23499,7 @@
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>2811</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -23502,7 +23508,7 @@
       <c r="C22" s="9" t="s">
         <v>2813</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>2814</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -23510,7 +23516,7 @@
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>2815</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -23519,7 +23525,7 @@
       <c r="C23" s="9" t="s">
         <v>2817</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="19" t="s">
         <v>2818</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -23527,7 +23533,7 @@
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>2819</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -23536,7 +23542,7 @@
       <c r="C24" s="9" t="s">
         <v>2821</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="19" t="s">
         <v>2822</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -23544,7 +23550,7 @@
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>2823</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -23553,7 +23559,7 @@
       <c r="C25" s="9" t="s">
         <v>2825</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="19" t="s">
         <v>2826</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -23561,7 +23567,7 @@
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>2827</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -23570,7 +23576,7 @@
       <c r="C26" s="9" t="s">
         <v>2829</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="19" t="s">
         <v>2830</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -23578,7 +23584,7 @@
       </c>
     </row>
     <row r="27" ht="31" customHeight="1">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>2831</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -23587,7 +23593,7 @@
       <c r="C27" s="9" t="s">
         <v>2833</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="19" t="s">
         <v>2834</v>
       </c>
       <c r="E27" s="13" t="s">
@@ -23595,7 +23601,7 @@
       </c>
     </row>
     <row r="28" ht="31" customHeight="1">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>2835</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -23604,7 +23610,7 @@
       <c r="C28" s="9" t="s">
         <v>2837</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="19" t="s">
         <v>2838</v>
       </c>
       <c r="E28" s="13" t="s">
@@ -23612,7 +23618,7 @@
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>2839</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -23621,7 +23627,7 @@
       <c r="C29" s="9" t="s">
         <v>2841</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="19" t="s">
         <v>2842</v>
       </c>
       <c r="E29" s="13" t="s">
@@ -23629,7 +23635,7 @@
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>2843</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -23638,7 +23644,7 @@
       <c r="C30" s="9" t="s">
         <v>2845</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="19" t="s">
         <v>2846</v>
       </c>
       <c r="E30" s="13" t="s">
@@ -23646,7 +23652,7 @@
       </c>
     </row>
     <row r="31" ht="31" customHeight="1">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>2847</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -23655,7 +23661,7 @@
       <c r="C31" s="9" t="s">
         <v>2849</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="19" t="s">
         <v>2850</v>
       </c>
       <c r="E31" s="13" t="s">
